--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487029_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487029_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3375</v>
+        <v>5.0131</v>
       </c>
       <c r="E2" t="n">
-        <v>3.9365</v>
+        <v>4.1457</v>
       </c>
       <c r="F2" t="n">
-        <v>1.4009</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="G2" t="n">
         <v>3.841</v>
@@ -610,13 +610,13 @@
         <v>1.0267</v>
       </c>
       <c r="S2" t="n">
-        <v>0.4697</v>
+        <v>0.1454</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.6587</v>
+        <v>-0.4495</v>
       </c>
       <c r="U2" t="n">
-        <v>1.1284</v>
+        <v>0.5949</v>
       </c>
       <c r="V2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>E. STOILOV</t>
+          <t>L. TVRDIC</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,67 +643,67 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0046</v>
+        <v>3.4091</v>
       </c>
       <c r="E3" t="n">
-        <v>3.6258</v>
+        <v>4.9736</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.6212</v>
+        <v>-1.5645</v>
       </c>
       <c r="G3" t="n">
-        <v>3.6331</v>
+        <v>2.6031</v>
       </c>
       <c r="H3" t="n">
-        <v>3.8277</v>
+        <v>-0.8986</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1946</v>
+        <v>3.5017</v>
       </c>
       <c r="J3" t="n">
-        <v>4.6371</v>
+        <v>5.3728</v>
       </c>
       <c r="K3" t="n">
-        <v>4.3214</v>
+        <v>0.5713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3157</v>
+        <v>4.8014</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.0041</v>
+        <v>-2.7697</v>
       </c>
       <c r="N3" t="n">
-        <v>-0.4937</v>
+        <v>-1.47</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.5104</v>
+        <v>-1.2997</v>
       </c>
       <c r="P3" t="n">
-        <v>0.616</v>
+        <v>2.0534</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.6427</v>
+        <v>2.0534</v>
       </c>
       <c r="S3" t="n">
-        <v>0.2832</v>
+        <v>-0.0688</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2249</v>
+        <v>-0.3992</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5081</v>
+        <v>0.3304</v>
       </c>
       <c r="V3" t="n">
-        <v>-1.5277</v>
+        <v>-1.1786</v>
       </c>
       <c r="W3" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X3" t="n">
-        <v>-1.7679</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="4">
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9081</v>
+        <v>2.5036</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3191</v>
+        <v>3.7961</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.411</v>
+        <v>-1.2924</v>
       </c>
       <c r="G4" t="n">
         <v>0.5359</v>
@@ -766,13 +766,13 @@
         <v>2.0534</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6677999999999999</v>
+        <v>0.2634</v>
       </c>
       <c r="T4" t="n">
-        <v>0.5384</v>
+        <v>0.0154</v>
       </c>
       <c r="U4" t="n">
-        <v>0.1295</v>
+        <v>0.248</v>
       </c>
       <c r="V4" t="n">
         <v>-0.3491</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. TVRDIC</t>
+          <t>E. STOILOV</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.8498</v>
+        <v>2.4899</v>
       </c>
       <c r="E5" t="n">
-        <v>4.3847</v>
+        <v>3.3779</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.5349</v>
+        <v>-0.8879</v>
       </c>
       <c r="G5" t="n">
-        <v>2.6031</v>
+        <v>3.6331</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.8986</v>
+        <v>3.8277</v>
       </c>
       <c r="I5" t="n">
-        <v>3.5017</v>
+        <v>-0.1946</v>
       </c>
       <c r="J5" t="n">
-        <v>5.3728</v>
+        <v>4.6371</v>
       </c>
       <c r="K5" t="n">
-        <v>0.5713</v>
+        <v>4.3214</v>
       </c>
       <c r="L5" t="n">
-        <v>4.8014</v>
+        <v>0.3157</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.7697</v>
+        <v>-1.0041</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.47</v>
+        <v>-0.4937</v>
       </c>
       <c r="O5" t="n">
-        <v>-1.2997</v>
+        <v>-0.5104</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0534</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0534</v>
+        <v>1.6427</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.6281</v>
+        <v>-0.2315</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.9881</v>
+        <v>-0.4728</v>
       </c>
       <c r="U5" t="n">
-        <v>0.36</v>
+        <v>0.2413</v>
       </c>
       <c r="V5" t="n">
-        <v>-1.1786</v>
+        <v>-1.5277</v>
       </c>
       <c r="W5" t="n">
-        <v>0</v>
+        <v>0.2402</v>
       </c>
       <c r="X5" t="n">
-        <v>-1.1786</v>
+        <v>-1.7679</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.5327</v>
+        <v>2.0153</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3166</v>
+        <v>0.5916</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2161</v>
+        <v>1.4236</v>
       </c>
       <c r="G6" t="n">
         <v>1.5261</v>
@@ -922,13 +922,13 @@
         <v>0.8214</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.8148</v>
+        <v>-0.3322</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.7905</v>
+        <v>-0.5154</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0243</v>
+        <v>0.1832</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>1.0705</v>
+        <v>1.8076</v>
       </c>
       <c r="E7" t="n">
-        <v>0.3158</v>
+        <v>0.9046999999999999</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7547</v>
+        <v>0.9029</v>
       </c>
       <c r="G7" t="n">
         <v>1.7706</v>
@@ -1000,13 +1000,13 @@
         <v>2.0534</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.7884</v>
+        <v>-0.0513</v>
       </c>
       <c r="T7" t="n">
-        <v>-1.054</v>
+        <v>-0.4651</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2655</v>
+        <v>0.4137</v>
       </c>
       <c r="V7" t="n">
         <v>-0.9384</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.1258</v>
+        <v>0.5346</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.0411</v>
+        <v>-0.766</v>
       </c>
       <c r="F8" t="n">
-        <v>0.9153</v>
+        <v>1.3006</v>
       </c>
       <c r="G8" t="n">
         <v>1.2717</v>
@@ -1078,13 +1078,13 @@
         <v>1.0267</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1573</v>
+        <v>-0.4969</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.9222</v>
+        <v>-0.6471</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2351</v>
+        <v>0.1502</v>
       </c>
       <c r="V8" t="n">
         <v>-0.2402</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>N. ZIZIC</t>
+          <t>J. SOLARIN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.2734</v>
+        <v>-0.7059</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.6835</v>
+        <v>0.2181</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4101</v>
+        <v>-0.924</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.9629</v>
+        <v>0.5248</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.7104</v>
+        <v>-0.4381</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2525</v>
+        <v>0.9629</v>
       </c>
       <c r="J9" t="n">
-        <v>0.3783</v>
+        <v>2.8446</v>
       </c>
       <c r="K9" t="n">
-        <v>0.2599</v>
+        <v>0.9767</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1184</v>
+        <v>1.8679</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.3412</v>
+        <v>-2.3198</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.9703000000000001</v>
+        <v>-1.4148</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3709</v>
+        <v>-0.905</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.8481</v>
+        <v>-1.6427</v>
       </c>
       <c r="Q9" t="n">
         <v>-3.0801</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>1.4374</v>
       </c>
       <c r="S9" t="n">
-        <v>1.8867</v>
+        <v>0.0629</v>
       </c>
       <c r="T9" t="n">
-        <v>1.3675</v>
+        <v>-0.1357</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5192</v>
+        <v>0.1986</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.3491</v>
+        <v>0.3491</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.3491</v>
+        <v>0.5893</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.2402</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>J. SOLARIN</t>
+          <t>I. RUIZ GONZALEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.3179</v>
+        <v>-1.8946</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.3049</v>
+        <v>-0.8633</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.013</v>
+        <v>-1.0313</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5248</v>
+        <v>-0.9354</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.4381</v>
+        <v>-0.6197</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9629</v>
+        <v>-0.3157</v>
       </c>
       <c r="J10" t="n">
-        <v>2.8446</v>
+        <v>0.0984</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9767</v>
+        <v>0.0195</v>
       </c>
       <c r="L10" t="n">
-        <v>1.8679</v>
+        <v>0.0789</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.3198</v>
+        <v>-1.0338</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4148</v>
+        <v>-0.6392</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.905</v>
+        <v>-0.3947</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.6427</v>
+        <v>0.4107</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.549</v>
+        <v>-0.0823</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.6587</v>
+        <v>-0.2635</v>
       </c>
       <c r="U10" t="n">
-        <v>0.1097</v>
+        <v>0.1811</v>
       </c>
       <c r="V10" t="n">
-        <v>0.3491</v>
+        <v>-1.2875</v>
       </c>
       <c r="W10" t="n">
-        <v>0.5893</v>
+        <v>-0.6982</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.2402</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="11">
@@ -1267,13 +1267,13 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.7792</v>
+        <v>-2.1227</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.1108</v>
+        <v>-1.4246</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.6684</v>
+        <v>-0.6981000000000001</v>
       </c>
       <c r="G11" t="n">
         <v>-1.9416</v>
@@ -1312,13 +1312,13 @@
         <v>0.616</v>
       </c>
       <c r="S11" t="n">
-        <v>0.3328</v>
+        <v>-0.0107</v>
       </c>
       <c r="T11" t="n">
-        <v>0.3021</v>
+        <v>-0.0117</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0307</v>
+        <v>0.001</v>
       </c>
       <c r="V11" t="n">
         <v>0.2402</v>
@@ -1333,7 +1333,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>I. RUIZ GONZALEZ</t>
+          <t>N. ZIZIC</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8056</v>
+        <v>-2.3194</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.8633</v>
+        <v>-2.7295</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9424</v>
+        <v>0.4101</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.9354</v>
+        <v>-0.9629</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.6197</v>
+        <v>-0.7104</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.3157</v>
+        <v>-0.2525</v>
       </c>
       <c r="J12" t="n">
-        <v>0.0984</v>
+        <v>0.3783</v>
       </c>
       <c r="K12" t="n">
-        <v>0.0195</v>
+        <v>0.2599</v>
       </c>
       <c r="L12" t="n">
-        <v>0.0789</v>
+        <v>0.1184</v>
       </c>
       <c r="M12" t="n">
-        <v>-1.0338</v>
+        <v>-1.3412</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.6392</v>
+        <v>-0.9703000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.3947</v>
+        <v>-0.3709</v>
       </c>
       <c r="P12" t="n">
-        <v>0.4107</v>
+        <v>-1.8481</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>-3.0801</v>
       </c>
       <c r="R12" t="n">
-        <v>0.4107</v>
+        <v>1.2321</v>
       </c>
       <c r="S12" t="n">
-        <v>0.0066</v>
+        <v>0.8407</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.2635</v>
+        <v>0.3214</v>
       </c>
       <c r="U12" t="n">
-        <v>0.2701</v>
+        <v>0.5192</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2875</v>
+        <v>-0.3491</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.6982</v>
+        <v>-0.3491</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.5893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>10.4013</v>
+        <v>10.7306</v>
       </c>
       <c r="E13" t="n">
-        <v>11.8949</v>
+        <v>12.2243</v>
       </c>
       <c r="F13" t="n">
-        <v>-1.4938</v>
+        <v>-1.4936</v>
       </c>
       <c r="G13" t="n">
         <v>11.8664</v>
@@ -1438,7 +1438,7 @@
         <v>7.1189</v>
       </c>
       <c r="I13" t="n">
-        <v>4.747500000000001</v>
+        <v>4.7475</v>
       </c>
       <c r="J13" t="n">
         <v>23.5925</v>
@@ -1447,13 +1447,13 @@
         <v>14.4388</v>
       </c>
       <c r="L13" t="n">
-        <v>9.1538</v>
+        <v>9.153799999999999</v>
       </c>
       <c r="M13" t="n">
         <v>-11.7262</v>
       </c>
       <c r="N13" t="n">
-        <v>-7.320100000000001</v>
+        <v>-7.320099999999999</v>
       </c>
       <c r="O13" t="n">
         <v>-4.4063</v>
@@ -1468,13 +1468,13 @@
         <v>14.3739</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.2908</v>
+        <v>0.03869999999999996</v>
       </c>
       <c r="T13" t="n">
-        <v>-3.3526</v>
+        <v>-3.0232</v>
       </c>
       <c r="U13" t="n">
-        <v>3.0618</v>
+        <v>3.0616</v>
       </c>
       <c r="V13" t="n">
         <v>-5.2813</v>
@@ -1483,7 +1483,7 @@
         <v>1.9217</v>
       </c>
       <c r="X13" t="n">
-        <v>-7.202900000000001</v>
+        <v>-7.2029</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.1728</v>
+        <v>3.722</v>
       </c>
       <c r="E14" t="n">
-        <v>3.8168</v>
+        <v>3.9214</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.644</v>
+        <v>-0.1994</v>
       </c>
       <c r="G14" t="n">
         <v>2.4692</v>
@@ -1546,13 +1546,13 @@
         <v>1.6427</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.0911</v>
+        <v>0.4582</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.2985</v>
+        <v>-0.1939</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2074</v>
+        <v>0.652</v>
       </c>
       <c r="V14" t="n">
         <v>0.5893</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>1.1463</v>
+        <v>1.2805</v>
       </c>
       <c r="E15" t="n">
-        <v>4.7822</v>
+        <v>4.8868</v>
       </c>
       <c r="F15" t="n">
-        <v>-3.6359</v>
+        <v>-3.6062</v>
       </c>
       <c r="G15" t="n">
         <v>3.0172</v>
@@ -1624,13 +1624,13 @@
         <v>0.8214</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.3986</v>
+        <v>-0.2644</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.4457</v>
+        <v>-0.341</v>
       </c>
       <c r="U15" t="n">
-        <v>0.047</v>
+        <v>0.0766</v>
       </c>
       <c r="V15" t="n">
         <v>-0.2402</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>0.4371</v>
+        <v>0.3778</v>
       </c>
       <c r="E16" t="n">
         <v>-1.7082</v>
       </c>
       <c r="F16" t="n">
-        <v>2.1453</v>
+        <v>2.086</v>
       </c>
       <c r="G16" t="n">
         <v>-0.4191</v>
@@ -1702,13 +1702,13 @@
         <v>1.2321</v>
       </c>
       <c r="S16" t="n">
-        <v>0.3634</v>
+        <v>0.3042</v>
       </c>
       <c r="T16" t="n">
         <v>-0.3062</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6696</v>
+        <v>0.6103</v>
       </c>
       <c r="V16" t="n">
         <v>0.6982</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>S. KANE</t>
+          <t>P. SALA VALLMAJO</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.4301</v>
+        <v>0.3649</v>
       </c>
       <c r="E17" t="n">
-        <v>0.242</v>
+        <v>0.1471</v>
       </c>
       <c r="F17" t="n">
-        <v>0.1881</v>
+        <v>0.2178</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.3111</v>
+        <v>-0.3906</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.0034</v>
+        <v>-0.117</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.3077</v>
+        <v>-0.2736</v>
       </c>
       <c r="J17" t="n">
-        <v>1.0906</v>
+        <v>0.7322</v>
       </c>
       <c r="K17" t="n">
-        <v>1.0512</v>
+        <v>0.7981</v>
       </c>
       <c r="L17" t="n">
-        <v>0.0395</v>
+        <v>-0.0659</v>
       </c>
       <c r="M17" t="n">
-        <v>-1.4017</v>
+        <v>-1.1228</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.0546</v>
+        <v>-0.9151</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.3472</v>
+        <v>-0.2077</v>
       </c>
       <c r="P17" t="n">
-        <v>0.4107</v>
+        <v>1.4374</v>
       </c>
       <c r="Q17" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
         <v>1.4374</v>
       </c>
       <c r="S17" t="n">
-        <v>0.3305</v>
+        <v>-0.6819</v>
       </c>
       <c r="T17" t="n">
-        <v>0.1781</v>
+        <v>-0.5851</v>
       </c>
       <c r="U17" t="n">
-        <v>0.1524</v>
+        <v>-0.0968</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>P. SALA VALLMAJO</t>
+          <t>S. KANE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,58 +1813,58 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.1278</v>
+        <v>-0.1958</v>
       </c>
       <c r="E18" t="n">
-        <v>0.1471</v>
+        <v>-0.1764</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.0193</v>
+        <v>-0.0194</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.3906</v>
+        <v>-0.3111</v>
       </c>
       <c r="H18" t="n">
-        <v>-0.117</v>
+        <v>-0.0034</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.2736</v>
+        <v>-0.3077</v>
       </c>
       <c r="J18" t="n">
-        <v>0.7322</v>
+        <v>1.0906</v>
       </c>
       <c r="K18" t="n">
-        <v>0.7981</v>
+        <v>1.0512</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.0659</v>
+        <v>0.0395</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.1228</v>
+        <v>-1.4017</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.9151</v>
+        <v>-1.0546</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.2077</v>
+        <v>-0.3472</v>
       </c>
       <c r="P18" t="n">
-        <v>1.4374</v>
+        <v>0.4107</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R18" t="n">
         <v>1.4374</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.919</v>
+        <v>-0.2954</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5851</v>
+        <v>-0.2403</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3339</v>
+        <v>-0.0551</v>
       </c>
       <c r="V18" t="n">
         <v>0</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. MIKHAILOV PALTARAK</t>
+          <t>X. TORRENT BAYÉ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6064</v>
+        <v>-1.6146</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.2942</v>
+        <v>-0.3532</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.3121</v>
+        <v>-1.2614</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.5197</v>
+        <v>0.3852</v>
       </c>
       <c r="H19" t="n">
-        <v>-1.294</v>
+        <v>-0.1754</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.2258</v>
+        <v>0.5606</v>
       </c>
       <c r="J19" t="n">
-        <v>0.8522999999999999</v>
+        <v>3.502</v>
       </c>
       <c r="K19" t="n">
-        <v>0.7339</v>
+        <v>1.713</v>
       </c>
       <c r="L19" t="n">
-        <v>0.1184</v>
+        <v>1.789</v>
       </c>
       <c r="M19" t="n">
-        <v>-3.372</v>
+        <v>-3.1168</v>
       </c>
       <c r="N19" t="n">
-        <v>-2.0279</v>
+        <v>-1.8884</v>
       </c>
       <c r="O19" t="n">
-        <v>-1.3441</v>
+        <v>-1.2284</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.616</v>
+        <v>-2.4641</v>
       </c>
       <c r="Q19" t="n">
-        <v>-1.4374</v>
+        <v>-3.2855</v>
       </c>
       <c r="R19" t="n">
         <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>1.5294</v>
+        <v>0.1153</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2985</v>
+        <v>-0.5697</v>
       </c>
       <c r="U19" t="n">
-        <v>1.8278</v>
+        <v>0.6849</v>
       </c>
       <c r="V19" t="n">
-        <v>0</v>
+        <v>0.3491</v>
       </c>
       <c r="W19" t="n">
-        <v>0.5893</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-0.5893</v>
+        <v>0.3491</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>X. TORRENT BAYÉ</t>
+          <t>D. EFAMBE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.6442</v>
+        <v>-1.9461</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3532</v>
+        <v>-1.751</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2911</v>
+        <v>-0.1951</v>
       </c>
       <c r="G20" t="n">
-        <v>0.3852</v>
+        <v>-0.9688</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.1754</v>
+        <v>-0.7136</v>
       </c>
       <c r="I20" t="n">
-        <v>0.5606</v>
+        <v>-0.2552</v>
       </c>
       <c r="J20" t="n">
-        <v>3.502</v>
+        <v>-0.6584</v>
       </c>
       <c r="K20" t="n">
-        <v>1.713</v>
+        <v>-0.6584</v>
       </c>
       <c r="L20" t="n">
-        <v>1.789</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>-3.1168</v>
+        <v>-0.3104</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.8884</v>
+        <v>-0.0552</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.2284</v>
+        <v>-0.2552</v>
       </c>
       <c r="P20" t="n">
-        <v>-2.4641</v>
+        <v>-1.0267</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.2855</v>
+        <v>-1.0267</v>
       </c>
       <c r="R20" t="n">
-        <v>0.8214</v>
+        <v>0</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0856</v>
+        <v>0.0494</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5697</v>
+        <v>-0.0659</v>
       </c>
       <c r="U20" t="n">
-        <v>0.6553</v>
+        <v>0.1153</v>
       </c>
       <c r="V20" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3491</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. EFAMBE</t>
+          <t>M. MIKHAILOV PALTARAK</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.9757</v>
+        <v>-2.1835</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.751</v>
+        <v>-0.1896</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.2247</v>
+        <v>-1.9939</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.9688</v>
+        <v>-2.5197</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.7136</v>
+        <v>-1.294</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2552</v>
+        <v>-1.2258</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.6584</v>
+        <v>0.8522999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.6584</v>
+        <v>0.7339</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>0.1184</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.3104</v>
+        <v>-3.372</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.0552</v>
+        <v>-2.0279</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.2552</v>
+        <v>-1.3441</v>
       </c>
       <c r="P21" t="n">
-        <v>-1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.0267</v>
+        <v>-1.4374</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>0.8214</v>
       </c>
       <c r="S21" t="n">
-        <v>0.0198</v>
+        <v>0.9522</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.0659</v>
+        <v>-0.1939</v>
       </c>
       <c r="U21" t="n">
-        <v>0.0856</v>
+        <v>1.146</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5893</v>
       </c>
       <c r="X21" t="n">
-        <v>0</v>
+        <v>-0.5893</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.8577</v>
+        <v>-2.6938</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.3861</v>
+        <v>-0.2815</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.4716</v>
+        <v>-2.4124</v>
       </c>
       <c r="G22" t="n">
         <v>-7.5157</v>
@@ -2170,13 +2170,13 @@
         <v>1.4374</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0318</v>
+        <v>0.1957</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.4883</v>
+        <v>-0.3837</v>
       </c>
       <c r="U22" t="n">
-        <v>0.5201</v>
+        <v>0.5794</v>
       </c>
       <c r="V22" t="n">
         <v>5.6529</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-7.6312</v>
+        <v>-7.5127</v>
       </c>
       <c r="E23" t="n">
         <v>-3.0017</v>
       </c>
       <c r="F23" t="n">
-        <v>-4.6295</v>
+        <v>-4.5109</v>
       </c>
       <c r="G23" t="n">
         <v>-5.613</v>
@@ -2248,13 +2248,13 @@
         <v>0.616</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.661</v>
+        <v>-0.5424</v>
       </c>
       <c r="T23" t="n">
         <v>-0.1822</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.4788</v>
+        <v>-0.3603</v>
       </c>
       <c r="V23" t="n">
         <v>-1.7679</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-10.4011</v>
+        <v>-10.4013</v>
       </c>
       <c r="E24" t="n">
-        <v>1.493700000000001</v>
+        <v>1.493699999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-11.8948</v>
+        <v>-11.8949</v>
       </c>
       <c r="G24" t="n">
         <v>-11.8664</v>
@@ -2305,7 +2305,7 @@
         <v>7.319899999999999</v>
       </c>
       <c r="L24" t="n">
-        <v>4.4064</v>
+        <v>4.406400000000001</v>
       </c>
       <c r="M24" t="n">
         <v>-23.5927</v>
@@ -2326,13 +2326,13 @@
         <v>10.2672</v>
       </c>
       <c r="S24" t="n">
-        <v>0.2907999999999999</v>
+        <v>0.2909000000000002</v>
       </c>
       <c r="T24" t="n">
-        <v>-3.062</v>
+        <v>-3.061900000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>3.3525</v>
+        <v>3.3523</v>
       </c>
       <c r="V24" t="n">
         <v>5.2814</v>
